--- a/MCD.xlsx
+++ b/MCD.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugol\Downloads\EPSI SN2\Projet Solution Applicative\Projet-Solution-Applicative\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF36BBC-BF56-481F-ABFD-E36FF4AAAE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,184 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="57">
+  <si>
+    <t>nom</t>
+  </si>
+  <si>
+    <t>prenom</t>
+  </si>
+  <si>
+    <t>date de naissance</t>
+  </si>
+  <si>
+    <t>adresse 1</t>
+  </si>
+  <si>
+    <t>adresse 2</t>
+  </si>
+  <si>
+    <t>ville</t>
+  </si>
+  <si>
+    <t>pays</t>
+  </si>
+  <si>
+    <t>statue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">argent </t>
+  </si>
+  <si>
+    <t xml:space="preserve">prix unique ? Ou </t>
+  </si>
+  <si>
+    <t>Livre</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>ID unique du livre</t>
+  </si>
+  <si>
+    <t>id du livre correspond</t>
+  </si>
+  <si>
+    <t>chaque livre phisique a un id different, mais peut avoir meme nom</t>
+  </si>
+  <si>
+    <t>statut abonnement</t>
+  </si>
+  <si>
+    <t>date fin abonnement</t>
+  </si>
+  <si>
+    <t>mineur, majeur, mineur verifié, majeur verifié (verifier = peut commander)</t>
+  </si>
+  <si>
+    <t>abonnement</t>
+  </si>
+  <si>
+    <t>type d'abonnement</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>tarif</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>numero</t>
+  </si>
+  <si>
+    <t>mail</t>
+  </si>
+  <si>
+    <t>nom du livre</t>
+  </si>
+  <si>
+    <t>année de publication</t>
+  </si>
+  <si>
+    <t>langue</t>
+  </si>
+  <si>
+    <t>auteur</t>
+  </si>
+  <si>
+    <t>genre</t>
+  </si>
+  <si>
+    <t>resumé</t>
+  </si>
+  <si>
+    <t>Titre périodique</t>
+  </si>
+  <si>
+    <t>mois</t>
+  </si>
+  <si>
+    <t>annee</t>
+  </si>
+  <si>
+    <t>jour</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>qutodient, herbdo, mensuel, annuel</t>
+  </si>
+  <si>
+    <t>semaine</t>
+  </si>
+  <si>
+    <t>donnée calculable pour hebdo</t>
+  </si>
+  <si>
+    <t>document sonore</t>
+  </si>
+  <si>
+    <t>titre</t>
+  </si>
+  <si>
+    <t>catégeorie</t>
+  </si>
+  <si>
+    <t>date de parution</t>
+  </si>
+  <si>
+    <t>cd, livre</t>
+  </si>
+  <si>
+    <t>chelouuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuu</t>
+  </si>
+  <si>
+    <t>car livre donc livre de livre ou autre ?</t>
+  </si>
+  <si>
+    <t>DVD et Blu-Ray</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>etudiant, employé, employé biblio, chomeur, admin</t>
+  </si>
+  <si>
+    <t>Document</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Auteur</t>
+  </si>
+  <si>
+    <t>Résumé</t>
+  </si>
+  <si>
+    <t>Genre</t>
+  </si>
+  <si>
+    <t>Langue</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>livre, dvd, ..</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -29,12 +211,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,8 +237,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +529,376 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K67"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="18.88671875" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="4"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="F16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="F17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="F18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="F19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="F20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="F21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F31" t="s">
+        <v>35</v>
+      </c>
+      <c r="G31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F32" t="s">
+        <v>37</v>
+      </c>
+      <c r="G32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="E34" t="s">
+        <v>39</v>
+      </c>
+      <c r="F34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="F35" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="F36" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="F37" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="F38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="F39" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="F40" t="s">
+        <v>41</v>
+      </c>
+      <c r="G40" t="s">
+        <v>43</v>
+      </c>
+      <c r="H40" t="s">
+        <v>44</v>
+      </c>
+      <c r="K40" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="E43" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>28</v>
+      </c>
+      <c r="B56" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B61" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>18</v>
+      </c>
+      <c r="B65" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B66" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B67" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:A13"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
--- a/MCD.xlsx
+++ b/MCD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugol\Downloads\EPSI SN2\Projet Solution Applicative\Projet-Solution-Applicative\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF36BBC-BF56-481F-ABFD-E36FF4AAAE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC530FFD-EF8E-4871-9E7B-8BE3EA64FFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="65">
   <si>
     <t>nom</t>
   </si>
@@ -90,9 +90,6 @@
     <t>description</t>
   </si>
   <si>
-    <t>tarif</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -102,78 +99,30 @@
     <t>mail</t>
   </si>
   <si>
-    <t>nom du livre</t>
-  </si>
-  <si>
-    <t>année de publication</t>
-  </si>
-  <si>
-    <t>langue</t>
-  </si>
-  <si>
     <t>auteur</t>
   </si>
   <si>
     <t>genre</t>
   </si>
   <si>
-    <t>resumé</t>
-  </si>
-  <si>
     <t>Titre périodique</t>
   </si>
   <si>
-    <t>mois</t>
-  </si>
-  <si>
-    <t>annee</t>
-  </si>
-  <si>
-    <t>jour</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
     <t>qutodient, herbdo, mensuel, annuel</t>
   </si>
   <si>
-    <t>semaine</t>
-  </si>
-  <si>
-    <t>donnée calculable pour hebdo</t>
-  </si>
-  <si>
     <t>document sonore</t>
   </si>
   <si>
-    <t>titre</t>
-  </si>
-  <si>
-    <t>catégeorie</t>
-  </si>
-  <si>
-    <t>date de parution</t>
-  </si>
-  <si>
-    <t>cd, livre</t>
-  </si>
-  <si>
-    <t>chelouuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuuu</t>
-  </si>
-  <si>
-    <t>car livre donc livre de livre ou autre ?</t>
-  </si>
-  <si>
     <t>DVD et Blu-Ray</t>
   </si>
   <si>
     <t>user</t>
   </si>
   <si>
-    <t>etudiant, employé, employé biblio, chomeur, admin</t>
-  </si>
-  <si>
     <t>Document</t>
   </si>
   <si>
@@ -186,9 +135,6 @@
     <t>Résumé</t>
   </si>
   <si>
-    <t>Genre</t>
-  </si>
-  <si>
     <t>Langue</t>
   </si>
   <si>
@@ -196,6 +142,84 @@
   </si>
   <si>
     <t>livre, dvd, ..</t>
+  </si>
+  <si>
+    <t>ou description</t>
+  </si>
+  <si>
+    <t>nombre de page</t>
+  </si>
+  <si>
+    <t>ISBN</t>
+  </si>
+  <si>
+    <t>code barre</t>
+  </si>
+  <si>
+    <t>numéro</t>
+  </si>
+  <si>
+    <t>date publication</t>
+  </si>
+  <si>
+    <t>durée</t>
+  </si>
+  <si>
+    <t>format audio</t>
+  </si>
+  <si>
+    <t>mp3, cd, .. ?</t>
+  </si>
+  <si>
+    <t>interprete</t>
+  </si>
+  <si>
+    <t>Question : ets ce que les livres numerique on un ISBN ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">format video </t>
+  </si>
+  <si>
+    <t>dvd, blueray</t>
+  </si>
+  <si>
+    <t>realisateur</t>
+  </si>
+  <si>
+    <t>note/description</t>
+  </si>
+  <si>
+    <t>disponnibilité</t>
+  </si>
+  <si>
+    <t>client</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>situation</t>
+  </si>
+  <si>
+    <t>admin, blibliothequaire ou maison des abonnées</t>
+  </si>
+  <si>
+    <t>etudiant, employé, en recherche d'emploi</t>
+  </si>
+  <si>
+    <t>annule, ou mensuel</t>
+  </si>
+  <si>
+    <t>abonnement - client</t>
+  </si>
+  <si>
+    <t>liaison</t>
+  </si>
+  <si>
+    <t>tarif mensuel</t>
+  </si>
+  <si>
+    <t>calcul du tarif annuel et en fonction de reduction</t>
   </si>
 </sst>
 </file>
@@ -211,7 +235,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -221,6 +245,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -237,19 +273,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -530,373 +567,353 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.88671875" customWidth="1"/>
     <col min="3" max="3" width="26.33203125" customWidth="1"/>
     <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>47</v>
+    <row r="1" spans="1:8" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="4"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
+      <c r="E1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="4"/>
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="4"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="4"/>
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
+      <c r="E4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="4"/>
       <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="4"/>
+      <c r="B9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="C9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="4"/>
       <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="4"/>
       <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+      <c r="D11" s="3"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="E13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="5"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E21" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E22" s="6"/>
+      <c r="F22" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E23" s="6"/>
+      <c r="F23" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I23" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="4" t="s">
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E24" s="6"/>
+      <c r="F24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G24" s="6"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E26" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E27" s="6"/>
+      <c r="F27" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G27" s="6"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E28" s="6"/>
+      <c r="F28" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E29" s="6"/>
+      <c r="F29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" s="6"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C16" s="4"/>
-      <c r="F16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="4"/>
-      <c r="F17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="4"/>
-      <c r="F18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="4"/>
-      <c r="F19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="F20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4" t="s">
+      <c r="B37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="F21" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E23" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F24" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F25" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F26" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F27" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F30" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F31" t="s">
-        <v>35</v>
-      </c>
-      <c r="G31" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F32" t="s">
-        <v>37</v>
-      </c>
-      <c r="G32" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="34" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="E34" t="s">
-        <v>39</v>
-      </c>
-      <c r="F34" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="F35" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="F36" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="F37" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="F38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="F39" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="F40" t="s">
-        <v>41</v>
-      </c>
-      <c r="G40" t="s">
-        <v>43</v>
-      </c>
-      <c r="H40" t="s">
-        <v>44</v>
-      </c>
-      <c r="K40" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="43" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="E43" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>28</v>
-      </c>
-      <c r="B56" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B57" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>11</v>
-      </c>
-      <c r="B60" t="s">
-        <v>12</v>
-      </c>
-      <c r="C60" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B61" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>18</v>
       </c>
-      <c r="B65" t="s">
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B43" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B44" t="s">
+        <v>63</v>
+      </c>
+      <c r="C44" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B66" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B67" t="s">
-        <v>21</v>
+      <c r="C48" t="s">
+        <v>60</v>
+      </c>
+      <c r="D48" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:A13"/>
+    <mergeCell ref="A1:A11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/MCD.xlsx
+++ b/MCD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugol\Downloads\EPSI SN2\Projet Solution Applicative\Projet-Solution-Applicative\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC530FFD-EF8E-4871-9E7B-8BE3EA64FFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D70CDF-7E7B-479B-8142-92923DF74485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="63">
   <si>
     <t>nom</t>
   </si>
@@ -51,12 +51,6 @@
     <t>statue</t>
   </si>
   <si>
-    <t xml:space="preserve">argent </t>
-  </si>
-  <si>
-    <t xml:space="preserve">prix unique ? Ou </t>
-  </si>
-  <si>
     <t>Livre</t>
   </si>
   <si>
@@ -87,9 +81,6 @@
     <t>type d'abonnement</t>
   </si>
   <si>
-    <t>description</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -120,24 +111,15 @@
     <t>DVD et Blu-Ray</t>
   </si>
   <si>
-    <t>user</t>
-  </si>
-  <si>
     <t>Document</t>
   </si>
   <si>
-    <t>Date</t>
-  </si>
-  <si>
     <t>Auteur</t>
   </si>
   <si>
     <t>Résumé</t>
   </si>
   <si>
-    <t>Langue</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -195,9 +177,6 @@
     <t>client</t>
   </si>
   <si>
-    <t>admin</t>
-  </si>
-  <si>
     <t>situation</t>
   </si>
   <si>
@@ -220,6 +199,21 @@
   </si>
   <si>
     <t>calcul du tarif annuel et en fonction de reduction</t>
+  </si>
+  <si>
+    <t>employe</t>
+  </si>
+  <si>
+    <t>utilisateur</t>
+  </si>
+  <si>
+    <t>année</t>
+  </si>
+  <si>
+    <t>hors année car gerer par document</t>
+  </si>
+  <si>
+    <t>pas d'interprete car auteur, sinon interprete facultatif</t>
   </si>
 </sst>
 </file>
@@ -567,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.88671875" customWidth="1"/>
@@ -578,20 +572,20 @@
   <sheetData>
     <row r="1" spans="1:8" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
       <c r="E1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -601,7 +595,7 @@
       </c>
       <c r="C2" s="1"/>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -618,13 +612,13 @@
       </c>
       <c r="C4" s="1"/>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F4" t="s">
         <v>7</v>
       </c>
       <c r="G4" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -651,269 +645,256 @@
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="1" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="E12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="3"/>
+      <c r="F12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="6"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>32</v>
-      </c>
+      <c r="A13" s="5"/>
       <c r="B13" s="5" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C13" s="5"/>
-      <c r="E13" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G13" s="6"/>
+        <v>35</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="5" t="s">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C14" s="5"/>
       <c r="E14" s="6"/>
       <c r="F14" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>42</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C15" s="5"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
-      <c r="B17" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>26</v>
-      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="E17" s="6"/>
       <c r="F17" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G17" s="6"/>
+        <v>38</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="5"/>
+        <v>31</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G18" s="6"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>28</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E21" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6" t="s">
+        <v>39</v>
+      </c>
       <c r="G21" s="6"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E22" s="6"/>
       <c r="F22" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G22" s="6"/>
+        <v>40</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I22" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E23" s="6"/>
       <c r="F23" s="6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I23" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E24" s="6"/>
-      <c r="F24" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G24" s="6"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E25" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E26" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6" t="s">
+        <v>39</v>
+      </c>
       <c r="G26" s="6"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E27" s="6"/>
       <c r="F27" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G27" s="6"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E28" s="6"/>
       <c r="F28" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E29" s="6"/>
-      <c r="F29" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G29" s="6"/>
+        <v>46</v>
+      </c>
+      <c r="G28" s="6"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>24</v>
-      </c>
       <c r="B33" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B35" t="s">
-        <v>53</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
         <v>11</v>
-      </c>
-      <c r="B37" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B39" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>18</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B44" t="s">
-        <v>63</v>
-      </c>
-      <c r="C44" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>61</v>
-      </c>
-      <c r="B48" t="s">
-        <v>19</v>
-      </c>
-      <c r="C48" t="s">
-        <v>60</v>
-      </c>
-      <c r="D48" t="s">
-        <v>62</v>
+        <v>56</v>
+      </c>
+      <c r="C43" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:A11"/>
+    <mergeCell ref="A1:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
